--- a/data/outputSpecialityRpt/File1/RPT_RPT7156946910381YQ_outputSpecialityRpt.xlsx
+++ b/data/outputSpecialityRpt/File1/RPT_RPT7156946910381YQ_outputSpecialityRpt.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Output| Specialty RPT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output| Specialty RPT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>55513071021</t>
+          <t>55513071001</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -877,51 +877,51 @@
         </is>
       </c>
       <c r="I15" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>3.261956810255907</v>
+        <v>1.087318936751969</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>3.35054996268899</v>
+        <v>1.116849987562997</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>3.459265268894496</v>
+        <v>1.153088422964832</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>3.536844688293491</v>
+        <v>1.178948229431164</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>3.613979449881758</v>
+        <v>1.204659816627253</v>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>$6751.56005859375</t>
+          <t>$2250.52001953125</t>
         </is>
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>$8090.394872082701</t>
+          <t>$2675.6603531859064</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>$8725.103171649751</t>
+          <t>$2943.9012373949695</t>
         </is>
       </c>
       <c r="R15" s="14" t="inlineStr">
         <is>
-          <t>$9454.015265212745</t>
+          <t>$3246.58014127411</t>
         </is>
       </c>
       <c r="S15" s="14" t="inlineStr">
         <is>
-          <t>$10142.179256673318</t>
+          <t>$3537.4331219582064</t>
         </is>
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>$10877.156895780538</t>
+          <t>$3853.181583567909</t>
         </is>
       </c>
       <c r="U15" s="14" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>58406003204</t>
+          <t>50881001060</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1017,101 +1017,101 @@
         </is>
       </c>
       <c r="I16" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>3.135399417044024</v>
+        <v>1.14544124098702</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>3.197828943521335</v>
+        <v>1.211056816097143</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>3.289284732828281</v>
+        <v>0.8267626857316338</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>3.361832477708115</v>
+        <v>0.5968334303712097</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>3.433904670054994</v>
+        <v>0.5967985949726635</v>
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>$88102.078125</t>
+          <t>$21120.0</t>
         </is>
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
-          <t>$95050.5962197075</t>
+          <t>$24420.09715427072</t>
         </is>
       </c>
       <c r="Q16" s="14" t="inlineStr">
         <is>
-          <t>$99421.30528385166</t>
+          <t>$26016.983342561383</t>
         </is>
       </c>
       <c r="R16" s="14" t="inlineStr">
         <is>
-          <t>$104834.19392788447</t>
+          <t>$17889.826824709176</t>
         </is>
       </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
-          <t>$109814.50770753021</t>
+          <t>$13005.17376356048</t>
         </is>
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>$114996.7603220133</t>
+          <t>$13099.662902590542</t>
         </is>
       </c>
       <c r="U16" s="14" t="inlineStr">
         <is>
-          <t>$95050.5962197075</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="V16" s="14" t="inlineStr">
         <is>
-          <t>$99421.30528385166</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="W16" s="14" t="inlineStr">
         <is>
-          <t>$104834.19392788447</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="X16" s="14" t="inlineStr">
         <is>
-          <t>$109814.50770753021</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Y16" s="14" t="inlineStr">
         <is>
-          <t>$114996.7603220133</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Z16" s="14" t="inlineStr">
         <is>
-          <t>$21964.10870014558</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AA16" s="14" t="inlineStr">
         <is>
-          <t>$22401.440192328802</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AB16" s="14" t="inlineStr">
         <is>
-          <t>$23042.10654146309</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AC16" s="14" t="inlineStr">
         <is>
-          <t>$23550.318205287844</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AD16" s="14" t="inlineStr">
         <is>
-          <t>$24055.198527188604</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>50881001060</t>
+          <t>55513071021</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1157,51 +1157,51 @@
         </is>
       </c>
       <c r="I17" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>1.14544124098702</v>
+        <v>3.261956810255907</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>1.211056816097143</v>
+        <v>3.35054996268899</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>0.8267626857316338</v>
+        <v>3.459265268894496</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.5968334303712097</v>
+        <v>3.536844688293491</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>0.5967985949726635</v>
+        <v>3.613979449881758</v>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>$21120.0</t>
+          <t>$6751.56005859375</t>
         </is>
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>$24420.09715427072</t>
+          <t>$8090.394872082701</t>
         </is>
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>$26016.983342561383</t>
+          <t>$8725.103171649751</t>
         </is>
       </c>
       <c r="R17" s="14" t="inlineStr">
         <is>
-          <t>$17889.826824709176</t>
+          <t>$9454.015265212745</t>
         </is>
       </c>
       <c r="S17" s="14" t="inlineStr">
         <is>
-          <t>$13005.17376356048</t>
+          <t>$10142.179256673318</t>
         </is>
       </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>$13099.662902590546</t>
+          <t>$10877.156895780536</t>
         </is>
       </c>
       <c r="U17" s="14" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>$64.65537946872068</t>
+          <t>$64.65537946872067</t>
         </is>
       </c>
       <c r="U18" s="14" t="inlineStr">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00006022761</t>
+          <t>NEWGENERICS50881001060</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC ISENTRESS</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1440,19 +1440,19 @@
         <v>0</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>2.40751414541765</v>
+        <v>0</v>
       </c>
       <c r="K19" s="14" t="n">
-        <v>2.26648199863115</v>
+        <v>0</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>2.063276219719166</v>
+        <v>0.4556848297977988</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>1.856256072233231</v>
+        <v>0.7511841320904425</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>1.667472793610844</v>
+        <v>0.8219601012643319</v>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
@@ -1461,27 +1461,27 @@
       </c>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>$17346.38001971529</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>$17137.08960751975</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R19" s="14" t="inlineStr">
         <is>
-          <t>$16334.344338281517</t>
+          <t>$8882.59763364207</t>
         </is>
       </c>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$15351.078574122135</t>
+          <t>$14755.910488278432</t>
         </is>
       </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>$14405.10530687558</t>
+          <t>$16271.010723827869</t>
         </is>
       </c>
       <c r="U19" s="14" t="inlineStr">
@@ -1553,75 +1553,75 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>55513071001</t>
+          <t>NEWGENERICS59676056201</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>NEW GENERIC PREZISTA</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I20" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>1.087318936751969</v>
+        <v>1.76125553811915</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>1.116849987562997</v>
+        <v>1.751767324460131</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>1.153088422964832</v>
+        <v>1.749786351114981</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>1.178948229431164</v>
+        <v>1.735767735036898</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>1.204659816627253</v>
+        <v>1.719248099140247</v>
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>$2250.52001953125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P20" s="14" t="inlineStr">
         <is>
-          <t>$2675.6603531859064</t>
+          <t>$13027.110988077866</t>
         </is>
       </c>
       <c r="Q20" s="14" t="inlineStr">
         <is>
-          <t>$2943.9012373949695</t>
+          <t>$13553.727764667197</t>
         </is>
       </c>
       <c r="R20" s="14" t="inlineStr">
         <is>
-          <t>$3246.58014127411</t>
+          <t>$14163.983046465342</t>
         </is>
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$3537.4331219582064</t>
+          <t>$14727.460065934401</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>$3853.18158356791</t>
+          <t>$15290.111912396334</t>
         </is>
       </c>
       <c r="U20" s="14" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>00069068803</t>
+          <t>50881000560</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -1717,101 +1717,101 @@
         </is>
       </c>
       <c r="I21" s="14" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>3.34373388931461</v>
+        <v>12.59985365085722</v>
       </c>
       <c r="K21" s="14" t="n">
-        <v>2.162341945141449</v>
+        <v>13.32162497706858</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>2.153975914873203</v>
+        <v>9.094389543047971</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>2.246219480843964</v>
+        <v>6.565167734083307</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>2.369353439304804</v>
+        <v>6.564784544699299</v>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>$237052.796875</t>
+          <t>$253440.0</t>
         </is>
       </c>
       <c r="P21" s="14" t="inlineStr">
         <is>
-          <t>$204556.77500006996</t>
+          <t>$293041.1658512486</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>$135665.30437921124</t>
+          <t>$312203.80011073657</t>
         </is>
       </c>
       <c r="R21" s="14" t="inlineStr">
         <is>
-          <t>$138535.9613856779</t>
+          <t>$214677.92189651018</t>
         </is>
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$148066.23352719384</t>
+          <t>$156062.08516272577</t>
         </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>$160120.67421652505</t>
+          <t>$157195.95483108654</t>
         </is>
       </c>
       <c r="U21" s="14" t="inlineStr">
         <is>
-          <t>$153417.58125005246</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="V21" s="14" t="inlineStr">
         <is>
-          <t>$135665.30437921124</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="W21" s="14" t="inlineStr">
         <is>
-          <t>$138535.9613856779</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="X21" s="14" t="inlineStr">
         <is>
-          <t>$148066.23352719384</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Y21" s="14" t="inlineStr">
         <is>
-          <t>$160120.67421652505</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Z21" s="14" t="inlineStr">
         <is>
-          <t>$103638.13432329954</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AA21" s="14" t="inlineStr">
         <is>
-          <t>$89361.6108545089</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AB21" s="14" t="inlineStr">
         <is>
-          <t>$89015.87370460626</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AC21" s="14" t="inlineStr">
         <is>
-          <t>$92827.959792393</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AD21" s="14" t="inlineStr">
         <is>
-          <t>$97916.63177772649</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -1833,75 +1833,75 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>61958190101</t>
+          <t>NEWGENERICS00006022761</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>NEW GENERIC ISENTRESS</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I22" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>3.269524076413061</v>
+        <v>2.40751414541765</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>3.413150240056282</v>
+        <v>2.26648199863115</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>3.561892538059612</v>
+        <v>2.063276219719166</v>
       </c>
       <c r="M22" s="14" t="n">
-        <v>3.709127855005549</v>
+        <v>1.856256072233232</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>3.860116052895251</v>
+        <v>1.667472793610845</v>
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>$45533.8798828125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P22" s="14" t="inlineStr">
         <is>
-          <t>$53195.712724811725</t>
+          <t>$17346.38001971529</t>
         </is>
       </c>
       <c r="Q22" s="14" t="inlineStr">
         <is>
-          <t>$58647.740568944224</t>
+          <t>$17137.08960751975</t>
         </is>
       </c>
       <c r="R22" s="14" t="inlineStr">
         <is>
-          <t>$64609.36611430518</t>
+          <t>$16334.344338281517</t>
         </is>
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$71008.47065235334</t>
+          <t>$15351.078574122137</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>$78017.84784231917</t>
+          <t>$14405.105306875577</t>
         </is>
       </c>
       <c r="U22" s="14" t="inlineStr">
@@ -1973,75 +1973,75 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>00006022761</t>
+          <t>NEWGENERICS50881000560</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>ISENTRESS</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I23" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" s="14" t="n">
-        <v>0.1283085548260666</v>
+        <v>0</v>
       </c>
       <c r="K23" s="14" t="n">
-        <v>0.04258839286573688</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>0.03870435936300515</v>
+        <v>5.012533127775788</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>0.03490022882701123</v>
+        <v>8.263025452994869</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>0.03145098360834658</v>
+        <v>9.041561113907653</v>
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>$22498.5615234375</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>$1026.793594142965</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q23" s="14" t="inlineStr">
         <is>
-          <t>$357.6327106341914</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R23" s="14" t="inlineStr">
         <is>
-          <t>$340.13714912623055</t>
+          <t>$106591.17160370485</t>
         </is>
       </c>
       <c r="S23" s="14" t="inlineStr">
         <is>
-          <t>$320.1641443648764</t>
+          <t>$177070.92585934117</t>
         </is>
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>$301.2731627303685</t>
+          <t>$195252.1286859344</t>
         </is>
       </c>
       <c r="U23" s="14" t="inlineStr">
@@ -2113,17 +2113,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>59676056201</t>
+          <t>00006022761</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>ISENTRESS</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -2140,48 +2140,48 @@
         <v>3</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>1.217192490284854</v>
+        <v>0.1283085548260666</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>1.215143212769734</v>
+        <v>0.04258839286573688</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>1.211712538387685</v>
+        <v>0.03870435936300515</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>1.204742038813293</v>
+        <v>0.03490022882701123</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>1.197088048792683</v>
+        <v>0.03145098360834658</v>
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>$23308.01953125</t>
+          <t>$22498.5615234375</t>
         </is>
       </c>
       <c r="P24" s="14" t="inlineStr">
         <is>
-          <t>$9999.367588661733</t>
+          <t>$1026.793594142965</t>
         </is>
       </c>
       <c r="Q24" s="14" t="inlineStr">
         <is>
-          <t>$10441.694719497129</t>
+          <t>$357.6327106341914</t>
         </is>
       </c>
       <c r="R24" s="14" t="inlineStr">
         <is>
-          <t>$10888.042957973712</t>
+          <t>$340.13714912623055</t>
         </is>
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>$11338.972939974046</t>
+          <t>$320.1641443648764</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
-          <t>$11805.020346401125</t>
+          <t>$301.2731627303684</t>
         </is>
       </c>
       <c r="U24" s="14" t="inlineStr">
@@ -2253,125 +2253,125 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS59676056201</t>
+          <t>58406003204</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC PREZISTA</t>
+          <t>ENBREL SURECLICK</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>1.76125553811915</v>
+        <v>3.135399417044024</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>1.751767324460131</v>
+        <v>3.197828943521335</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>1.749786351114981</v>
+        <v>3.289284732828281</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>1.735767735036898</v>
+        <v>3.361832477708115</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>1.719248099140246</v>
+        <v>3.433904670054994</v>
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$88102.078125</t>
         </is>
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>$13027.110988077866</t>
+          <t>$95050.5962197075</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>$13553.727764667197</t>
+          <t>$99421.30528385166</t>
         </is>
       </c>
       <c r="R25" s="14" t="inlineStr">
         <is>
-          <t>$14163.983046465342</t>
+          <t>$104834.19392788447</t>
         </is>
       </c>
       <c r="S25" s="14" t="inlineStr">
         <is>
-          <t>$14727.4600659344</t>
+          <t>$109814.50770753021</t>
         </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>$15290.111912396338</t>
+          <t>$114996.76032201329</t>
         </is>
       </c>
       <c r="U25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$95050.5962197075</t>
         </is>
       </c>
       <c r="V25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$99421.30528385166</t>
         </is>
       </c>
       <c r="W25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$104834.19392788447</t>
         </is>
       </c>
       <c r="X25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$109814.50770753021</t>
         </is>
       </c>
       <c r="Y25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$114996.76032201329</t>
         </is>
       </c>
       <c r="Z25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$21964.10870014558</t>
         </is>
       </c>
       <c r="AA25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$22401.440192328802</t>
         </is>
       </c>
       <c r="AB25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23042.10654146309</t>
         </is>
       </c>
       <c r="AC25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23550.318205287844</t>
         </is>
       </c>
       <c r="AD25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$24055.198527188604</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881000560</t>
+          <t>00069068803</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>IBRANCE</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2408,110 +2408,110 @@
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I26" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>0</v>
+        <v>3.34373388931461</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0</v>
+        <v>2.162341945141449</v>
       </c>
       <c r="L26" s="14" t="n">
-        <v>5.012533127775788</v>
+        <v>2.153975914873203</v>
       </c>
       <c r="M26" s="14" t="n">
-        <v>8.263025452994867</v>
+        <v>2.246219480843964</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>9.041561113907649</v>
+        <v>2.369353439304804</v>
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$237052.796875</t>
         </is>
       </c>
       <c r="P26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$204556.77500006996</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$135665.30437921124</t>
         </is>
       </c>
       <c r="R26" s="14" t="inlineStr">
         <is>
-          <t>$106591.17160370485</t>
+          <t>$138535.9613856779</t>
         </is>
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>$177070.92585934114</t>
+          <t>$148066.23352719384</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>$195252.12868593447</t>
+          <t>$160120.674216525</t>
         </is>
       </c>
       <c r="U26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$153417.58125005246</t>
         </is>
       </c>
       <c r="V26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$135665.30437921124</t>
         </is>
       </c>
       <c r="W26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$138535.9613856779</t>
         </is>
       </c>
       <c r="X26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$148066.23352719384</t>
         </is>
       </c>
       <c r="Y26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$160120.674216525</t>
         </is>
       </c>
       <c r="Z26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$103638.13432329954</t>
         </is>
       </c>
       <c r="AA26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$89361.6108545089</t>
         </is>
       </c>
       <c r="AB26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$89015.87370460626</t>
         </is>
       </c>
       <c r="AC26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$92827.959792393</t>
         </is>
       </c>
       <c r="AD26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$97916.63177772649</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
         <v>2.959764318325942</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>3.143570417129167</v>
+        <v>3.143570417129168</v>
       </c>
       <c r="N27" s="14" t="n">
         <v>3.305337151730743</v>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="S27" s="14" t="inlineStr">
         <is>
-          <t>$186802.9031628855</t>
+          <t>$186802.90316288552</t>
         </is>
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>$201448.84966839082</t>
+          <t>$201448.8496683908</t>
         </is>
       </c>
       <c r="U27" s="14" t="inlineStr">
@@ -2673,75 +2673,75 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS49702022813</t>
+          <t>59676056201</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC TIVICAY</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>0</v>
+        <v>1.217192490284854</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0.2679033920902113</v>
+        <v>1.215143212769734</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>1.228456205077303</v>
+        <v>1.211712538387685</v>
       </c>
       <c r="M28" s="14" t="n">
-        <v>1.2083195692084</v>
+        <v>1.204742038813293</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>1.115228172138178</v>
+        <v>1.197088048792683</v>
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23308.01953125</t>
         </is>
       </c>
       <c r="P28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$9999.367588661733</t>
         </is>
       </c>
       <c r="Q28" s="14" t="inlineStr">
         <is>
-          <t>$772.6764577630839</t>
+          <t>$10441.694719497129</t>
         </is>
       </c>
       <c r="R28" s="14" t="inlineStr">
         <is>
-          <t>$3741.4591499830344</t>
+          <t>$10888.042957973712</t>
         </is>
       </c>
       <c r="S28" s="14" t="inlineStr">
         <is>
-          <t>$3869.4651350843783</t>
+          <t>$11338.972939974046</t>
         </is>
       </c>
       <c r="T28" s="14" t="inlineStr">
         <is>
-          <t>$3755.092675117231</t>
+          <t>$11805.020346401123</t>
         </is>
       </c>
       <c r="U28" s="14" t="inlineStr">
@@ -2813,17 +2813,17 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>50881000560</t>
+          <t>61958190101</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -2837,51 +2837,51 @@
         </is>
       </c>
       <c r="I29" s="14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>12.59985365085722</v>
+        <v>3.269524076413061</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>13.32162497706858</v>
+        <v>3.413150240056282</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>9.094389543047971</v>
+        <v>3.561892538059612</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>6.565167734083307</v>
+        <v>3.709127855005549</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>6.564784544699299</v>
+        <v>3.860116052895251</v>
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>$253440.0</t>
+          <t>$45533.8798828125</t>
         </is>
       </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t>$293041.1658512486</t>
+          <t>$53195.712724811725</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>$312203.80011073657</t>
+          <t>$58647.740568944224</t>
         </is>
       </c>
       <c r="R29" s="14" t="inlineStr">
         <is>
-          <t>$214677.92189651018</t>
+          <t>$64609.36611430518</t>
         </is>
       </c>
       <c r="S29" s="14" t="inlineStr">
         <is>
-          <t>$156062.08516272577</t>
+          <t>$71008.47065235334</t>
         </is>
       </c>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>$157195.95483108656</t>
+          <t>$78017.84784231914</t>
         </is>
       </c>
       <c r="U29" s="14" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881001060</t>
+          <t>NEWGENERICS49702022813</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>NEW GENERIC TIVICAY</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2983,16 +2983,16 @@
         <v>0</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>0</v>
+        <v>0.2679033920902113</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>0.4556848297977988</v>
+        <v>1.228456205077303</v>
       </c>
       <c r="M30" s="14" t="n">
-        <v>0.7511841320904424</v>
+        <v>1.2083195692084</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>0.8219601012643317</v>
+        <v>1.115228172138179</v>
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
@@ -3006,22 +3006,22 @@
       </c>
       <c r="Q30" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$772.6764577630839</t>
         </is>
       </c>
       <c r="R30" s="14" t="inlineStr">
         <is>
-          <t>$8882.59763364207</t>
+          <t>$3741.4591499830344</t>
         </is>
       </c>
       <c r="S30" s="14" t="inlineStr">
         <is>
-          <t>$14755.91048827843</t>
+          <t>$3869.4651350843787</t>
         </is>
       </c>
       <c r="T30" s="14" t="inlineStr">
         <is>
-          <t>$16271.010723827872</t>
+          <t>$3755.09267511723</t>
         </is>
       </c>
       <c r="U30" s="14" t="inlineStr">
